--- a/readmission_records.xlsx
+++ b/readmission_records.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W10"/>
+  <dimension ref="A1:W18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1434,6 +1434,814 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Asian</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Middle-aged</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Respiratory</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>40</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>15</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Diabetes</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>2026-03-01 11:08:06</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>79.19%</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>High Risk</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>raj</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Asian</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Young</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>40</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>15</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Diabetes</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>8</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>2026-03-01 11:22:20</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>81.21%</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>High Risk</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>laddu</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Asian</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Young</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>40</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>15</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Diabetes</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>4</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>2026-03-01 11:22:34</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>71.38%</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>High Risk</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>laddu</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Asian</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Young</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>40</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>15</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Diabetes</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>4</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2026-03-01 11:22:37</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>71.38%</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>High Risk</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>laddu</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Asian</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Young</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Digestive</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>40</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>15</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Diabetes</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>4</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>2026-03-01 11:22:46</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>72.40%</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>High Risk</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>laddu</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Young</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>9</v>
+      </c>
+      <c r="E16" t="n">
+        <v>15</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Neoplasms</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>40</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>15</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Diabetes</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>15</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>2026-03-01 12:04:29</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>77.90%</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>High Risk</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>jyo</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Young</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>9</v>
+      </c>
+      <c r="E17" t="n">
+        <v>15</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Genitourinary</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>40</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>15</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Diabetes</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>15</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>2026-03-01 12:04:37</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>81.49%</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>High Risk</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>jyo</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Young</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>9</v>
+      </c>
+      <c r="E18" t="n">
+        <v>15</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Diabetes</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>40</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>15</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Diabetes</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>15</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>2026-03-01 12:04:48</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>85.08%</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>High Risk</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>jyo</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
